--- a/04_Modules/01_Build/c_data/01_build.xlsx
+++ b/04_Modules/01_Build/c_data/01_build.xlsx
@@ -11692,7 +11692,7 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Preprocess/03_Quantification/c_data/DAList_corrected.rds</t>
+    <t>01_Preprocess/03_Quantify/c_data/DAList_corrected.rds</t>
   </si>
   <si>
     <t>88b8d60d5a5dd59c66bf102ba6a7c4d5</t>
